--- a/.netlify/blobs-serve/entries/unlinked/site:ledgerly-users/ledgerly-users.xlsx
+++ b/.netlify/blobs-serve/entries/unlinked/site:ledgerly-users/ledgerly-users.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -463,9 +463,23 @@
         <v>2ad0288de7ee781af892d7311533312d:1d1a004adccd35f81ffa05080fbc516b344ef80f4d22c46296d8a123a45a657ae2e2bcef1946eee3e7e0ec84cd8d06b8e5c4e380f1871d2ea24270a22fbd914f</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>aaaa</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-08-28T19:03:57.888Z</v>
+      </c>
+      <c r="C6" t="str">
+        <v>aaaa</v>
+      </c>
+      <c r="D6" t="str">
+        <v>31f7b00e3ef57e7bd7d696e677c0bf17:06599989845b5b5037b832b3600814d51e732a7cdac77489c22befbcd527771ffad2853392f0dad0336463828b37a83f31ab88c013ee045eb7e166babb8b17cf</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/.netlify/blobs-serve/entries/unlinked/site:ledgerly-users/ledgerly-users.xlsx
+++ b/.netlify/blobs-serve/entries/unlinked/site:ledgerly-users/ledgerly-users.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Profiles" sheetId="1" r:id="rId1"/>
+    <sheet name="Settings" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -482,4 +483,43 @@
     <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Profile</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Categories</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Default Currency</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Theme Preference</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>aaaa</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Food, Transport, Entertainment, Shopping, Bills, Other</v>
+      </c>
+      <c r="C2" t="str">
+        <v>LKR</v>
+      </c>
+      <c r="D2" t="str">
+        <v>dark</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+  </ignoredErrors>
+</worksheet>
 </file>